--- a/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="347">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -323,10 +323,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -362,7 +362,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
+    <t>リソースコンテンツの言語</t>
   </si>
   <si>
     <t>リソースが書かれている基本言語。</t>
@@ -374,7 +374,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -420,7 +420,7 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
+    <t>含まれている、インラインのリソース</t>
   </si>
   <si>
     <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
@@ -465,7 +465,7 @@
     <t>Condition.modifierExtension</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
+    <t>無視できない拡張機能</t>
   </si>
   <si>
     <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
@@ -487,10 +487,10 @@
     <t>この状態の外部ID。</t>
   </si>
   <si>
-    <t>サーバーからサーバーへ伝搬するにつれて更新され、パフォーマーまたは他のシステムによって割り当てられたビジネス識別子が、この状態に対して一定の値を保持します。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません（[discussion]（resource.html＃identifiers）を参照）。 識別子が単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じ識別子を持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。</t>
+    <t>サーバーからサーバーへ伝搬するにつれて更新され、パフォーマーまたは他のシステムによって割り当てられたビジネスidentifierが、この状態に対して一定の値を保持します。</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません（[discussion]（resource.html＃identifiers）を参照）。 identifierが単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じidentifierを持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。</t>
   </si>
   <si>
     <t>Allows identification of the condition as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -715,10 +715,7 @@
     <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。</t>
   </si>
   <si>
-    <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1004,7 +1001,7 @@
 </t>
   </si>
   <si>
-    <t>「評価の公式記録」</t>
+    <t>評価の公式記録</t>
   </si>
   <si>
     <t>ステージング評価の根拠となる正式な証拠記録への参照。</t>
@@ -1016,7 +1013,7 @@
     <t>Condition.stage.type</t>
   </si>
   <si>
-    <t>"演出の種類" (Enshutsu no shurui)</t>
+    <t>演出の種類</t>
   </si>
   <si>
     <t>病理的ステージングや臨床ステージングといった種類のステージング</t>
@@ -1452,8 +1449,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.6171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="30.75" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3462,11 +3459,9 @@
       <c r="X17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Y17" s="2"/>
+      <c r="Z17" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -3502,31 +3497,31 @@
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AM17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3545,17 +3540,17 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3604,7 +3599,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>92</v>
@@ -3619,19 +3614,19 @@
         <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -3639,10 +3634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3665,16 +3660,16 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3724,7 +3719,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -3739,19 +3734,19 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>80</v>
@@ -3759,10 +3754,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3785,16 +3780,16 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3844,7 +3839,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -3859,19 +3854,19 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
@@ -3879,10 +3874,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3905,16 +3900,16 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3964,7 +3959,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -3973,7 +3968,7 @@
         <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>104</v>
@@ -3988,10 +3983,10 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -3999,10 +3994,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4025,13 +4020,13 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4082,7 +4077,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4103,13 +4098,13 @@
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -4117,10 +4112,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4143,13 +4138,13 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4200,7 +4195,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4224,10 +4219,10 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -4235,10 +4230,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4261,13 +4256,13 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4318,7 +4313,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4339,13 +4334,13 @@
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -4353,10 +4348,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4379,13 +4374,13 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4436,7 +4431,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4448,19 +4443,19 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>80</v>
@@ -4471,10 +4466,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4497,13 +4492,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4554,7 +4549,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4578,7 +4573,7 @@
         <v>80</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
@@ -4589,10 +4584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4621,7 +4616,7 @@
         <v>139</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>141</v>
@@ -4674,7 +4669,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4698,7 +4693,7 @@
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
@@ -4709,14 +4704,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4738,10 +4733,10 @@
         <v>138</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>141</v>
@@ -4796,7 +4791,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4831,10 +4826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4860,10 +4855,10 @@
         <v>159</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4893,11 +4888,11 @@
         <v>208</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
       </c>
@@ -4914,7 +4909,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4923,7 +4918,7 @@
         <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>104</v>
@@ -4932,7 +4927,7 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>169</v>
@@ -4949,10 +4944,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4975,13 +4970,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5032,7 +5027,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5041,7 +5036,7 @@
         <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>104</v>
@@ -5056,7 +5051,7 @@
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>80</v>
@@ -5067,10 +5062,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5096,10 +5091,10 @@
         <v>159</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5129,11 +5124,11 @@
         <v>208</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>317</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5150,7 +5145,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5174,7 +5169,7 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -5185,10 +5180,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5211,16 +5206,16 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5270,7 +5265,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5282,19 +5277,19 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -5305,10 +5300,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5331,13 +5326,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5388,7 +5383,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5412,7 +5407,7 @@
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -5423,10 +5418,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5455,7 +5450,7 @@
         <v>139</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>141</v>
@@ -5508,7 +5503,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5532,7 +5527,7 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -5543,14 +5538,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5572,10 +5567,10 @@
         <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>141</v>
@@ -5630,7 +5625,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5665,10 +5660,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5694,10 +5689,10 @@
         <v>159</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5727,11 +5722,11 @@
         <v>208</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5748,7 +5743,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5757,13 +5752,13 @@
         <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>189</v>
@@ -5772,10 +5767,10 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
@@ -5783,10 +5778,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5809,13 +5804,13 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5866,7 +5861,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5875,7 +5870,7 @@
         <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -5890,10 +5885,10 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
@@ -5901,10 +5896,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5927,13 +5922,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5984,7 +5979,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5999,16 +5994,16 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>

--- a/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="348">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -459,7 +459,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.modifierExtension</t>
@@ -715,7 +715,10 @@
     <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS</t>
+    <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -773,7 +776,7 @@
 この患者状態の記録やレコード作成に関連する受療の状況（外来、入院、救急、在宅など）</t>
   </si>
   <si>
-    <t>通常、イベントが発生したEncounter（診察、受診、入退院など）の中で行われることが多いですが、公式的にEncounter（診察、受診、入退院など）が完了する前または後に開始される場合がありますが、それでもEncounter（診察、受診、入退院など）の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初のEncounter（診察、受診、入退院など）とは異なる場合があります。</t>
+    <t>通常、イベントが発生した受療行動の中で行われることが多いですが、公式的に受療行動が完了する前または後に開始される場合がありますが、それでも受療行動の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初の受療行動とは異なる場合があります。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1013,7 +1016,7 @@
     <t>Condition.stage.type</t>
   </si>
   <si>
-    <t>演出の種類</t>
+    <t>ステージングの種類</t>
   </si>
   <si>
     <t>病理的ステージングや臨床ステージングといった種類のステージング</t>
@@ -1060,7 +1063,7 @@
     <t>Condition.evidence.code</t>
   </si>
   <si>
-    <t>表れ/症状</t>
+    <t>判断した根拠となる兆候や症状</t>
   </si>
   <si>
     <t>この状態の記録に至った兆候や症状。</t>
@@ -1449,8 +1452,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="30.75" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.109375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3459,9 +3462,11 @@
       <c r="X17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Y17" s="2"/>
+      <c r="Y17" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -3497,31 +3502,31 @@
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3540,17 +3545,17 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3599,7 +3604,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>92</v>
@@ -3614,19 +3619,19 @@
         <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -3634,10 +3639,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3660,16 +3665,16 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3719,7 +3724,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -3734,19 +3739,19 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>80</v>
@@ -3754,10 +3759,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3780,16 +3785,16 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3839,7 +3844,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -3854,19 +3859,19 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
@@ -3874,10 +3879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3900,16 +3905,16 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3959,7 +3964,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -3968,7 +3973,7 @@
         <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>104</v>
@@ -3983,10 +3988,10 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -3994,10 +3999,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4020,13 +4025,13 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4077,7 +4082,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4098,13 +4103,13 @@
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -4112,10 +4117,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4138,13 +4143,13 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4195,7 +4200,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4219,10 +4224,10 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -4230,10 +4235,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4256,13 +4261,13 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4313,7 +4318,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4334,13 +4339,13 @@
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -4348,10 +4353,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4374,13 +4379,13 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4431,7 +4436,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4443,7 +4448,7 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
@@ -4455,7 +4460,7 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>80</v>
@@ -4466,10 +4471,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4492,13 +4497,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4549,7 +4554,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4573,7 +4578,7 @@
         <v>80</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
@@ -4584,10 +4589,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4616,7 +4621,7 @@
         <v>139</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>141</v>
@@ -4669,7 +4674,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4693,7 +4698,7 @@
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
@@ -4704,14 +4709,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4733,10 +4738,10 @@
         <v>138</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>141</v>
@@ -4791,7 +4796,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4826,10 +4831,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4855,10 +4860,10 @@
         <v>159</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4888,10 +4893,10 @@
         <v>208</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
@@ -4909,7 +4914,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4918,7 +4923,7 @@
         <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>104</v>
@@ -4927,7 +4932,7 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>169</v>
@@ -4944,10 +4949,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4970,13 +4975,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5027,7 +5032,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5036,7 +5041,7 @@
         <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>104</v>
@@ -5051,7 +5056,7 @@
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>80</v>
@@ -5062,10 +5067,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5091,10 +5096,10 @@
         <v>159</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5124,10 +5129,10 @@
         <v>208</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5145,7 +5150,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5169,7 +5174,7 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -5180,10 +5185,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5206,16 +5211,16 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5265,7 +5270,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5277,7 +5282,7 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
@@ -5289,7 +5294,7 @@
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -5300,10 +5305,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5326,13 +5331,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5383,7 +5388,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5407,7 +5412,7 @@
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -5418,10 +5423,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5450,7 +5455,7 @@
         <v>139</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>141</v>
@@ -5503,7 +5508,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5527,7 +5532,7 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -5538,14 +5543,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5567,10 +5572,10 @@
         <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>141</v>
@@ -5625,7 +5630,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5660,10 +5665,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5689,10 +5694,10 @@
         <v>159</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5722,10 +5727,10 @@
         <v>208</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5743,7 +5748,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5752,13 +5757,13 @@
         <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>189</v>
@@ -5767,10 +5772,10 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
@@ -5778,10 +5783,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5804,13 +5809,13 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5861,7 +5866,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5870,7 +5875,7 @@
         <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -5885,10 +5890,10 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
@@ -5896,10 +5901,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5922,13 +5927,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5979,7 +5984,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5994,16 +5999,16 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>

--- a/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
@@ -1428,17 +1428,17 @@
   <dimension ref="A1:AP38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.88671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="30.765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="185.2109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="158.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1447,28 +1447,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.6171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.96875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="68.20703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="222.1015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="58.4765625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="190.4140625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
@@ -377,7 +377,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -603,7 +603,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -673,7 +673,7 @@
     <t>状態や診断の特定</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -718,7 +718,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -987,7 +987,7 @@
     <t>状態段階を説明するコード（例：がんの段階）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1025,7 +1025,7 @@
     <t>状態分類を表すコード（例：臨床的または病理学的）。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1072,7 +1072,7 @@
     <t>症状や現れ方を記述するコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1091,7 +1091,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1453,7 +1453,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.96875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
